--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$62</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -1745,6 +1748,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2094,7 +2112,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2214,7 +2232,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>93</v>
       </c>
@@ -2334,7 +2352,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>101</v>
       </c>
@@ -2452,7 +2470,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>107</v>
       </c>
@@ -2572,7 +2590,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>113</v>
       </c>
@@ -2692,7 +2710,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>122</v>
       </c>
@@ -2812,7 +2830,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>130</v>
       </c>
@@ -2932,7 +2950,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>138</v>
       </c>
@@ -3052,7 +3070,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>146</v>
       </c>
@@ -3174,7 +3192,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>151</v>
       </c>
@@ -3193,7 +3211,7 @@
         <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>83</v>
@@ -3294,7 +3312,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>160</v>
       </c>
@@ -3416,7 +3434,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>170</v>
       </c>
@@ -3536,7 +3554,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>179</v>
       </c>
@@ -3658,7 +3676,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>192</v>
       </c>
@@ -3778,7 +3796,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>201</v>
       </c>
@@ -3900,7 +3918,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>216</v>
       </c>
@@ -4018,7 +4036,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>222</v>
       </c>
@@ -4138,7 +4156,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>228</v>
       </c>
@@ -4260,7 +4278,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>237</v>
       </c>
@@ -4378,7 +4396,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>238</v>
       </c>
@@ -4498,7 +4516,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>239</v>
       </c>
@@ -4620,7 +4638,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>248</v>
       </c>
@@ -4740,7 +4758,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>255</v>
       </c>
@@ -4860,7 +4878,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>263</v>
       </c>
@@ -4980,7 +4998,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>270</v>
       </c>
@@ -5102,7 +5120,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>279</v>
       </c>
@@ -5224,7 +5242,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>287</v>
       </c>
@@ -5243,7 +5261,7 @@
         <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>83</v>
@@ -5346,7 +5364,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>297</v>
       </c>
@@ -5466,7 +5484,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>303</v>
       </c>
@@ -5588,7 +5606,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>314</v>
       </c>
@@ -5710,7 +5728,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>325</v>
       </c>
@@ -5830,7 +5848,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>333</v>
       </c>
@@ -5952,7 +5970,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>343</v>
       </c>
@@ -5971,7 +5989,7 @@
         <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>83</v>
@@ -6074,7 +6092,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>353</v>
       </c>
@@ -6196,7 +6214,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>363</v>
       </c>
@@ -6318,7 +6336,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>375</v>
       </c>
@@ -6440,7 +6458,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>383</v>
       </c>
@@ -6560,7 +6578,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>393</v>
       </c>
@@ -6682,7 +6700,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>402</v>
       </c>
@@ -6802,7 +6820,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>411</v>
       </c>
@@ -6922,7 +6940,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>420</v>
       </c>
@@ -7044,7 +7062,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>429</v>
       </c>
@@ -7162,7 +7180,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>430</v>
       </c>
@@ -7282,7 +7300,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>431</v>
       </c>
@@ -7404,7 +7422,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>436</v>
       </c>
@@ -7522,7 +7540,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>443</v>
       </c>
@@ -7640,7 +7658,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>447</v>
       </c>
@@ -7762,7 +7780,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>456</v>
       </c>
@@ -7884,7 +7902,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>463</v>
       </c>
@@ -8004,7 +8022,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>469</v>
       </c>
@@ -8122,7 +8140,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>473</v>
       </c>
@@ -8242,7 +8260,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>480</v>
       </c>
@@ -8362,7 +8380,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>485</v>
       </c>
@@ -8484,7 +8502,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>492</v>
       </c>
@@ -8602,7 +8620,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>493</v>
       </c>
@@ -8722,7 +8740,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>494</v>
       </c>
@@ -8844,7 +8862,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>495</v>
       </c>
@@ -8966,7 +8984,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>500</v>
       </c>
@@ -9088,7 +9106,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>505</v>
       </c>
@@ -9210,7 +9228,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>509</v>
       </c>
@@ -9332,7 +9350,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>510</v>
       </c>
@@ -9455,6 +9473,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP62">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI61">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-18</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -285,7 +285,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -332,16 +332,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -467,7 +467,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -495,10 +495,10 @@
 </t>
   </si>
   <si>
-    <t>観察のためのビジネス識別子 / Business Identifier for observation</t>
-  </si>
-  <si>
-    <t>この観察に割り当てられた一意の識別子。 / A unique identifier assigned to this observation.</t>
+    <t>観察のためのビジネスidentifier / Business Identifier for observation</t>
+  </si>
+  <si>
+    <t>この観察に割り当てられた一意のidentifier。 / A unique identifier assigned to this observation.</t>
   </si>
   <si>
     <t>観測を区別し、参照することを可能にします。 / Allows observations to be distinguished and referenced.</t>
@@ -562,7 +562,7 @@
     <t>参照イベントの一部 / Part of referenced event</t>
   </si>
   <si>
-    <t>この特定の観察結果がコンポーネントまたはステップであるより大きなイベント。たとえば、手順の一部としての観察。 / A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
+    <t>この特定の観察結果がコンポーネントまたはステップであるより大きなイベント。たとえば、プロシジャー（処置等）の一部としての観察。 / A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
     <t>このObservation（所見）が生成される元になった画像検査</t>
@@ -1006,7 +1006,7 @@
     <t>観察のための臨床的に関連する時間/時間期 / Clinically relevant time/time-period for observation</t>
   </si>
   <si>
-    <t>観察された値が真実であると主張される時間または時間期。生物学的被験者の場合 - 例えばヒト患者 - これは通常、「生理学的に関連する時間」と呼ばれます。これは通常、手順または標本収集の時間ですが、日付/時刻のソースは不明であり、日付/時刻自体のみです。 / The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+    <t>観察された値が真実であると主張される時間または時間期。生物学的被験者の場合 - 例えばヒト患者 - これは通常、「生理学的に関連する時間」と呼ばれます。これは通常、プロシジャー（処置等）または標本収集の時間ですが、日付/時刻のソースは不明であり、日付/時刻自体のみです。 / The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
     <t>所見が生成された日時(DateTime)。</t>
@@ -1343,7 +1343,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の重要性を評価するのに役立ちます。さまざまなコンテキストに複数の参照範囲を提供できる必要があります。 / Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="527">
   <si>
     <t>Property</t>
   </si>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -495,10 +495,7 @@
 </t>
   </si>
   <si>
-    <t>観察のためのビジネスidentifier / Business Identifier for observation</t>
-  </si>
-  <si>
-    <t>この観察に割り当てられた一意のidentifier。 / A unique identifier assigned to this observation.</t>
+    <t>このObservationリソースの一意な識別ID</t>
   </si>
   <si>
     <t>観測を区別し、参照することを可能にします。 / Allows observations to be distinguished and referenced.</t>
@@ -527,10 +524,7 @@
 </t>
   </si>
   <si>
-    <t>計画、提案、または命令を満たします / Fulfills plan, proposal or order</t>
-  </si>
-  <si>
-    <t>このイベントによって全体または一部に満たされる計画、提案、または命令。たとえば、薬物療法では、患者が分配される前に臨床検査を実施する必要がある場合があります。 / A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
+    <t>このObservationが実施されることになった依頼や計画、提案に関する情報</t>
   </si>
   <si>
     <t>このObservationが生成されることになった画像検査に関するオーダ情報</t>
@@ -559,10 +553,7 @@
 </t>
   </si>
   <si>
-    <t>参照イベントの一部 / Part of referenced event</t>
-  </si>
-  <si>
-    <t>この特定の観察結果がコンポーネントまたはステップであるより大きなイベント。たとえば、プロシジャー（処置等）の一部としての観察。 / A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
+    <t>このObservationが親イベントの一部を成す要素であるとき、その親イベントに関する情報</t>
   </si>
   <si>
     <t>このObservation（所見）が生成される元になった画像検査</t>
@@ -580,13 +571,10 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>登録|予備|ファイナル|修正 + / registered | preliminary | final | amended +</t>
-  </si>
-  <si>
-    <t>結果値のステータス。 / The status of the result value.</t>
-  </si>
-  <si>
-    <t>この要素は、リソースを現在有効ではないとマークするコードが含まれているため、修飾子としてラベル付けされています。 / This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+    <t>結果の状態</t>
+  </si>
+  <si>
+    <t>このリソースは現在有効でないというマークをするコードを含んでいるため、この要素はモディファイアー（修飾的要素）として位置づけられている。</t>
   </si>
   <si>
     <t>個々の結果のステータスを追跡する必要があります。レポート全体が最終決定される前に、いくつかの結果が確定します。 / Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
@@ -623,7 +611,41 @@
 </t>
   </si>
   <si>
-    <t>観察の種類の分類 / Classification of  type of observation</t>
+    <t>このObservationを分類するコード</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
+  </si>
+  <si>
+    <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:coding.system}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>検査の第1カテゴリはJP_SimpleObservationCategory_VSから値を指定する。</t>
   </si>
   <si>
     <t>行われている一般的なタイプの観測を分類するコード。 / A code that classifies the general type of observation being made.</t>
@@ -632,16 +654,254 @@
     <t>このObservationを分類するコード。(imaging)が指定される。</t>
   </si>
   <si>
-    <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
+    <t>Observation.category:first.id</t>
+  </si>
+  <si>
+    <t>Observation.category.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.category:first.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.extension</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding</t>
+  </si>
+  <si>
+    <t>Observation.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.system</t>
+  </si>
+  <si>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.version</t>
+  </si>
+  <si>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.code</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>imaging</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.display</t>
+  </si>
+  <si>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Observation.category:first.text</t>
+  </si>
+  <si>
+    <t>Observation.category.text</t>
+  </si>
+  <si>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -651,10 +911,7 @@
 </t>
   </si>
   <si>
-    <t>観察の種類（コード /タイプ） / Type of observation (code / type)</t>
-  </si>
-  <si>
-    <t>観察されたものについて説明します。時々、これは観察「名前」と呼ばれます。 / Describes what was observed. Sometimes this is called the observation "name".</t>
+    <t>このObservationの対象を特定するコード</t>
   </si>
   <si>
     <t>observation(所見)を表すLOINCコード。18782-3, Radiology Study observation (narrative)が指定される。</t>
@@ -693,69 +950,12 @@
     <t>Observation.code.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.code.extension</t>
   </si>
   <si>
-    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
     <t>Observation.code.coding.id</t>
   </si>
   <si>
@@ -765,146 +965,25 @@
     <t>Observation.code.coding.system</t>
   </si>
   <si>
-    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
     <t>http://loinc.org</t>
   </si>
   <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
     <t>Observation.code.coding.version</t>
   </si>
   <si>
-    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
     <t>Observation.code.coding.code</t>
   </si>
   <si>
-    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
     <t>18782-3</t>
   </si>
   <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
     <t>Observation.code.coding.display</t>
   </si>
   <si>
-    <t>システムによって定義された表現 / Representation defined by the system</t>
-  </si>
-  <si>
-    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
     <t>Observation.code.coding.userSelected</t>
   </si>
   <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
     <t>Observation.code.text</t>
-  </si>
-  <si>
-    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -914,10 +993,7 @@
 </t>
   </si>
   <si>
-    <t>誰と/または観察が何であるか / Who and/or what the observation is about</t>
-  </si>
-  <si>
-    <t>患者、または患者のグループ、場所、またはデバイスこの観察結果は、観察が置かれている記録についてであり、その記録にあります。観測の実際の焦点が被験者（または被験者の部分、または領域のサンプル）とは異なる場合、「フォーカス」要素または「コード」自体が観測の実際の焦点を指定します。 / The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>このObservationの対象となる患者や患者群、機器、場所に関する情報</t>
   </si>
   <si>
     <t>このObservationの対象となる患者。</t>
@@ -945,13 +1021,10 @@
 </t>
   </si>
   <si>
-    <t>それが記録の主題に関するものではないとき、観察とは何か / What the observation is about, when it is not about the subject of record</t>
-  </si>
-  <si>
-    <t>配偶者、親、胎児、ドナーなどの患者に関連する何かまたは患者に関連する誰かを表す記録の患者ではない場合の観察の実際の焦点。たとえば、母親の記録における胎児の観察。観察の焦点は、既存の状態、介入、被験者の食事、被験者の別の観察、または腫瘍や移植装置などの身体構造でもあります。ユースケースの例は、観測リソースを使用して、母親が子供の気管切開チューブを変更するように訓練されているかどうかを把握することです。この例では、子供は記録の患者であり、母親は焦点です。 / The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
-  </si>
-  <si>
-    <t>通常、患者、または患者、場所、またはデバイスのグループである被験者について観察が行われ、被験者と観察のために直接測定されるものとの区別は、観察コード自体で指定されています（例えば、血液グルコース"）そして、この要素を使用して個別に表現する必要はありません。標本への参照が必要な場合は、「標本」を使用してください。リソースの代わりにコードが必要な場合、ボディサイトまたは標準拡張[FocusCode]（Extension-Observation-Focuscode.html）に「BodySite」を使用します。 / Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+    <t>配偶者、親、胎児、ドナーなど、このObservationのsubject要素が実際の対象でない場合、その実際の対象に関する情報</t>
+  </si>
+  <si>
+    <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -964,17 +1037,14 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
-    <t>この観察が行われるヘルスケアイベント / Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>この観察が行われるヘルスケアイベント（患者と医療提供者の相互作用など）。 / The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
-  </si>
-  <si>
-    <t>これは通常、イベントが発生したEncounterですが、いくつかのイベントは、Encounterの公式完了前または公式完了後に開始される可能性がありますが、それでも遭遇のコンテキストに関連しています（例：入院前の実験室テストなど）。 / This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
+    <t>診察や入院など、このObservationが実施されるきっかけとなった診療イベントに関する情報</t>
+  </si>
+  <si>
+    <t>通常、イベントが発生したEncounterであるが、一部のイベントは、Encounterの正式な完了の前または後に開始される場合があり、その場合でもEncounterのコンテキストに関連付けられている（例：入院前の臨床検査）。</t>
   </si>
   <si>
     <t>一部の観察では、観察と特定のEncounterの間のリンクを知ることが重要かもしれません。 / For some observations it may be important to know the link between an observation and a particular encounter.</t>
@@ -1003,10 +1073,7 @@
 </t>
   </si>
   <si>
-    <t>観察のための臨床的に関連する時間/時間期 / Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>観察された値が真実であると主張される時間または時間期。生物学的被験者の場合 - 例えばヒト患者 - これは通常、「生理学的に関連する時間」と呼ばれます。これは通常、プロシジャー（処置等）または標本収集の時間ですが、日付/時刻のソースは不明であり、日付/時刻自体のみです。 / The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+    <t>取得された結果が臨床的に確定された日時または期間</t>
   </si>
   <si>
     <t>所見が生成された日時(DateTime)。</t>
@@ -1034,10 +1101,7 @@
 </t>
   </si>
   <si>
-    <t>日付/時刻このバージョンが利用可能になりました / Date/Time this version was made available</t>
-  </si>
-  <si>
-    <t>このバージョンの観察結果は、通常、結果がレビューおよび検証された後にプロバイダーが利用できるようになりました。 / The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
+    <t>このバージョンのObservationが医療者に提供された日時。通常、結果を確認し検証後に提供される日時</t>
   </si>
   <si>
     <t>所見が確定された日時(DateTime)。参照元のDiagnosticReportの日時と一致する必要がある。</t>
@@ -1059,10 +1123,7 @@
 </t>
   </si>
   <si>
-    <t>観察の責任者 / Who is responsible for the observation</t>
-  </si>
-  <si>
-    <t>観察された値を「真」として主張する責任者。 / Who was responsible for asserting the observed value as "true".</t>
+    <t>このObservationの責任者/実施者に関する情報</t>
   </si>
   <si>
     <t>所見を生成した医療者。通常は読影医。</t>
@@ -1086,10 +1147,7 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>実結果 / Actual result</t>
-  </si>
-  <si>
-    <t>情報が単純な値を持っている場合、観察結果の結果として決定された情報。 / The information determined as a result of making the observation, if the information has a simple value.</t>
+    <t>取得された結果</t>
   </si>
   <si>
     <t>所見の内容。</t>
@@ -1117,15 +1175,10 @@
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
-    <t>結果が欠落している理由 / Why the result is missing</t>
-  </si>
-  <si>
-    <t>要素観測値の期待値が欠落している理由を提供します。 / Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
-  </si>
-  <si>
-    <t>NULLまたは例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されていない」、「決定的でない」、または「標本の不十分」である可能性があります。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。報告する値がある場合にのみ、観察が報告される可能性があることに注意してください。たとえば、異なるセルカウント値は、&gt; 0の場合にのみ報告される場合があります。これらのオプションのため、ヌルまたは例外的な値の一般的な観測を解釈するには、ユースケース契約が必要です。 / Null or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "specimen unsatisfactory".   
-The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed. Note that an observation may only be reported if there are values to report. For example differential cell counts values may be reported only when &gt; 0.  Because of these options, use-case agreements are required to interpret general observations for null or exceptional values.</t>
+    <t>このObservationのvalue[x]要素に期待される結果が存在しなかった場合、その理由</t>
+  </si>
+  <si>
+    <t>ヌル値または例外値は、FHIRオブザベーションで2つの方法で表すことができる。 1つの方法は、それらを値セットに含めて、値の例外を表す方法である。たとえば、血清学的検査の測定値は、「検出された」、「検出されなかった」、「決定的でない」、または「検体が不十分」である可能性がある。別の方法は、実際の観測にvalue要素を使用し、明示的なdataAbsentReason要素を使用して例外的な値を記録することである。たとえば、測定が完了しなかった場合、dataAbsentReasonコード「error」を使用できる。この場合には、観測値は、報告する値がある場合にのみ報告される可能性があることに注意する必要がある。たとえば、差分セルカウント値は&gt; 0の場合にのみ報告される場合がある。これらのオプションのため、nullまたは例外値の一般的な観測値を解釈するにはユースケースの合意が必要である。</t>
   </si>
   <si>
     <t>多くの結果には、測定で例外的な値を処理する必要があります。 / For many results it is necessary to handle exceptional values in measurements.</t>
@@ -1154,16 +1207,13 @@
 </t>
   </si>
   <si>
-    <t>高、低、正常など。 / High, low, normal, etc.</t>
-  </si>
-  <si>
-    <t>観測値のカテゴリー評価。たとえば、高、低、正常。 / A categorical assessment of an observation value.  For example, high, low, normal.</t>
-  </si>
-  <si>
-    <t>歴史的に実験室の結果（「異常なフラグ」と呼ばれる）に使用されていたため、その使用は、コード化された解釈が関連する他のユースケースにまで及びます。多くの場合、1つ以上の単純なコンパクトコードとして報告されているこの要素は、結果の意味/正常性のステータスを示すレポートとフローシートの結果値に隣接することがよくあります。 / Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
-  </si>
-  <si>
-    <t>いくつかの結果、特に数値の結果については、結果の重要性を完全に理解するために解釈が必要です。 / For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
+    <t>高、低、正常等の結果のカテゴリ分けした評価</t>
+  </si>
+  <si>
+    <t>「異常フラグ」として呼ばれる検査結果解釈コードが従来から使用されており、その使用はコード化された解釈が関連するような他の場合でも拡大して使われている。多くの場合、1つ以上の単純でコンパクトなコードとして報告され、この要素は、結果の意味や正常かどうかを示すために、レポートや時系列表で結果値の隣に配置されることがよくある。</t>
+  </si>
+  <si>
+    <t>一部の結果、特に数値結果については、結果の意義を完全に理解するためには解釈コードが必要である。</t>
   </si>
   <si>
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
@@ -1191,10 +1241,7 @@
 </t>
   </si>
   <si>
-    <t>観察についてのコメント / Comments about the observation</t>
-  </si>
-  <si>
-    <t>観察または結果についてのコメント。 / Comments about the observation or the results.</t>
+    <t>このObservationに関するコメント</t>
   </si>
   <si>
     <t>診断報告所の所見に記載されないコメント等。</t>
@@ -1212,10 +1259,7 @@
     <t>Observation.bodySite</t>
   </si>
   <si>
-    <t>観察された身体部分 / Observed body part</t>
-  </si>
-  <si>
-    <t>観察が行われた被験者の本体のサイト（つまり、ターゲットサイト）を示します。 / Indicates the site on the subject's body where the observation was made (i.e. the target site).</t>
+    <t>対象となった身体部位</t>
   </si>
   <si>
     <t>観察結果で見つかったコードで暗黙的ではない場合にのみ使用されます。多くのシステムでは、これはインラインコンポーネントの代わりに関連する観察として表される場合があります。
@@ -1223,10 +1267,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1244,10 +1285,7 @@
     <t>Observation.method</t>
   </si>
   <si>
-    <t>それがどのように行われたか / How it was done</t>
-  </si>
-  <si>
-    <t>観察を実行するために使用されるメカニズムを示します。 / Indicates the mechanism used to perform the observation.</t>
+    <t>このObservationの実施方法</t>
   </si>
   <si>
     <t>CODERATION.CODEのコードに暗黙的ではない場合にのみ使用されます。 / Only used if not implicit in code for Observation.code.</t>
@@ -1271,17 +1309,14 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>
-    <t>この観察に使用される標本 / Specimen used for this observation</t>
-  </si>
-  <si>
-    <t>この観察が行われたときに使用された標本。 / The specimen that was used when this observation was made.</t>
-  </si>
-  <si>
-    <t>「観察」で見つかったコードで暗黙的ではない場合にのみ使用する必要があります。観察は標本自体では行われません。それらは主題で作られていますが、多くの場合、標本の手段によって作られています。標本はしばしば関与していますが、それらは常に明示的に追跡され、報告されているわけではないことに注意してください。また、標本を明示的に追跡するコンテキストで観測リソースを使用できることに注意してください（例：診断レポート）。 / Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
+    <t>このObservationに使われた検体/標本に関する情報</t>
+  </si>
+  <si>
+    <t>`Observation.code`にあるコードで暗黙的に示されない場合にのみ使用する必要がある。検体自体の観察は行われない。観察（観測、検査）対象者に対して実施されるが、多くの場合には対象者から得られた検体に対して実施される。検体が奥の場合に関わるが、それらは常に追跡され、明示的に報告されるとは限らないことに注意すること。またobservationリソースは、検体を明示的に記述するような状況下（診断レポートなど）で使用される場合があることに注意。</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -1303,13 +1338,10 @@
 </t>
   </si>
   <si>
-    <t>（測定）デバイス / (Measurement) Device</t>
-  </si>
-  <si>
-    <t>観測データを生成するために使用されるデバイス。 / The device used to generate the observation data.</t>
-  </si>
-  <si>
-    <t>これは、結果の送信に関与するデバイス、たとえばゲートウェイを表すことを意図していないことに注意してください。このようなデバイスは、関連する出所リソースを使用して文書化される場合があります。 / Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
+    <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
+  </si>
+  <si>
+    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -1331,16 +1363,13 @@
 </t>
   </si>
   <si>
-    <t>解釈のためのガイドを提供します / Provides guide for interpretation</t>
-  </si>
-  <si>
-    <t>通常または推奨範囲と比較して、値を解釈する方法に関するガイダンス。複数の参照範囲は「または」として解釈されます。言い換えれば、2つの異なるターゲット集団を表すために、2つの「参照」要素が使用されます。 / Guidance on how to interpret the value by comparison to a normal or recommended range.  Multiple reference ranges are interpreted as an "OR".   In other words, to represent two distinct target populations, two `referenceRange` elements would be used.</t>
-  </si>
-  <si>
-    <t>ほとんどの観測には、一般的な参照範囲が1つしかありません。システムは、患者に関する知識（患者の年齢、性別、体重、その他の要因に固有）に基づいて、関連する参照範囲のみを供給することを制限することを選択できますが、これは不可能または適切ではない場合があります。複数の参照範囲が提供される場合は、それらの間の違いを参照範囲および/または年齢特性で提供する必要があります。 / Most observations only have one generic reference range. Systems MAY choose to restrict to only supplying the relevant reference range based on knowledge about the patient (e.g., specific to the patient's age, gender, weight and other factors), but this might not be possible or appropriate. Whenever more than one reference range is supplied, the differences between them SHOULD be provided in the reference range and/or age properties.</t>
-  </si>
-  <si>
-    <t>どの値が「正常」と見なされるかを知ることは、特定の結果の重要性を評価するのに役立ちます。さまざまなコンテキストに複数の参照範囲を提供できる必要があります。 / Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
+    <t>基準範囲との比較による結果の解釈方法のガイダンス</t>
+  </si>
+  <si>
+    <t>通常の範囲または推奨範囲と比較して値を解釈する方法に関するガイダンス。複数の参照範囲は「OR」として解釈される。つまり、2つの異なるターゲット母集団を表すために、2つの `referenceRange`要素が使用される。</t>
+  </si>
+  <si>
+    <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -1504,10 +1533,7 @@
 </t>
   </si>
   <si>
-    <t>観察グループに属する関連リソース / Related resource that belongs to the Observation group</t>
-  </si>
-  <si>
-    <t>この観察は、グループのメンバーとしてのターゲットを含むグループ観察（たとえば、バッテリー、テストのパネル、重要な兆候測定のセット）です。 / This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
+    <t>このObservationに関連する子リソースに関する情報。このObservationに関連する/属するパネル検査や検査セットなどのObservationグループ</t>
   </si>
   <si>
     <t>レポートの所見に関連する計測値等をObservationで保持する場合、ここに指定する。</t>
@@ -1522,10 +1548,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t>関連測定観測はから行われます / Related measurements the observation is made from</t>
-  </si>
-  <si>
-    <t>この観測値が導出される測定値を表すターゲットリソース。たとえば、超音波画像に基づいた計算された陰イオンギャップまたは胎児測定。 / The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
+    <t>このObservationの結果の導出元に関する情報。例えば、画像検査から取得された結果となる場合その導出元となる画像検査結果を示すImagingStudyリソース</t>
   </si>
   <si>
     <t>この所見の元となった画像検査。</t>
@@ -1537,16 +1560,13 @@
     <t>Observation.component</t>
   </si>
   <si>
-    <t>コンポーネントの結果 / Component results</t>
-  </si>
-  <si>
-    <t>一部の観察には、複数のコンポーネント観測があります。これらのコンポーネント観測は、同じ属性を共有する個別のコード値ペアとして表されます。例には、血圧測定のための収縮期および拡張期成分観察と、遺伝学の観察のための複数の成分観察が含まれます。 / Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
-  </si>
-  <si>
-    <t>観測をグループで一緒に組み立てる方法についての議論については、以下の[Notes]（obervation.html＃notes）を参照してください。 / For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>コンポーネント観測は、観測リソースで主要な観測と同じ属性を共有し、常に単一の観測の一部を扱われます（分離できません）。ただし、一次観測値の参照範囲はコンポーネント値によって継承されず、各コンポーネント観測に適切な場合は必要です。 / Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
+    <t>複合的な結果。例えば、血圧測定値ではそれを構成する収縮期および拡張期の値の組み合わせ</t>
+  </si>
+  <si>
+    <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
+  </si>
+  <si>
+    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1588,6 +1608,9 @@
   </si>
   <si>
     <t>実際のコンポーネントの結果 / Actual component result</t>
+  </si>
+  <si>
+    <t>情報が単純な値を持っている場合、観察結果の結果として決定された情報。 / The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
     <t>観察には一連のコンポーネント観測がある場合に使用されます。観察には、値（APGARスコアなど）とコンポーネントの観測（APGARスコアが導き出された観測）の両方があります。値が存在する場合、この要素のデータ型は、viscervation.codeによって決定する必要があります。フィールドが通常コーディングされている場合、または観測に関連付けられたタイプの場合、文字列の代わりにテキストのみを持つCodeableconecteが使用されます。コードはコード化された値を定義します。追加のガイダンスについては、以下の[[メモ]セクション]（[観察.html＃注）を参照してください。 / Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -1613,6 +1636,18 @@
     <t>Observation.component.interpretation</t>
   </si>
   <si>
+    <t>高、低、正常など。 / High, low, normal, etc.</t>
+  </si>
+  <si>
+    <t>観測値のカテゴリー評価。たとえば、高、低、正常。 / A categorical assessment of an observation value.  For example, high, low, normal.</t>
+  </si>
+  <si>
+    <t>歴史的に実験室の結果（「異常なフラグ」と呼ばれる）に使用されていたため、その使用は、コード化された解釈が関連する他のユースケースにまで及びます。多くの場合、1つ以上の単純なコンパクトコードとして報告されているこの要素は、結果の意味/正常性のステータスを示すレポートとフローシートの結果値に隣接することがよくあります。 / Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
+  </si>
+  <si>
+    <t>いくつかの結果、特に数値の結果については、結果の重要性を完全に理解するために解釈が必要です。 / For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
+  </si>
+  <si>
     <t>Observation.component.referenceRange</t>
   </si>
   <si>
@@ -1620,6 +1655,12 @@
   </si>
   <si>
     <t>通常または推奨範囲と比較して、値を解釈する方法に関するガイダンス。 / Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+  </si>
+  <si>
+    <t>ほとんどの観測には、一般的な参照範囲が1つしかありません。システムは、患者に関する知識（患者の年齢、性別、体重、その他の要因に固有）に基づいて、関連する参照範囲のみを供給することを制限することを選択できますが、これは不可能または適切ではない場合があります。複数の参照範囲が提供される場合は、それらの間の違いを参照範囲および/または年齢特性で提供する必要があります。 / Most observations only have one generic reference range. Systems MAY choose to restrict to only supplying the relevant reference range based on knowledge about the patient (e.g., specific to the patient's age, gender, weight and other factors), but this might not be possible or appropriate. Whenever more than one reference range is supplied, the differences between them SHOULD be provided in the reference range and/or age properties.</t>
+  </si>
+  <si>
+    <t>どの値が「正常」と見なされるかを知ることは、特定の結果の重要性を評価するのに役立ちます。さまざまなコンテキストに複数の参照範囲を提供できる必要があります。 / Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
 </sst>
 </file>
@@ -1938,7 +1979,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP62"/>
+  <dimension ref="A1:AP74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -3226,11 +3267,11 @@
         <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>83</v>
@@ -3294,19 +3335,19 @@
         <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>83</v>
@@ -3314,14 +3355,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3340,19 +3381,19 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>83</v>
@@ -3401,7 +3442,7 @@
         <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3416,16 +3457,16 @@
         <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>83</v>
@@ -3436,14 +3477,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3462,16 +3503,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3521,7 +3562,7 @@
         <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3536,16 +3577,16 @@
         <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>83</v>
@@ -3556,10 +3597,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3585,16 +3626,16 @@
         <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>83</v>
@@ -3619,13 +3660,13 @@
         <v>83</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>83</v>
@@ -3643,7 +3684,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>94</v>
@@ -3658,19 +3699,19 @@
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>83</v>
@@ -3678,10 +3719,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3689,7 +3730,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>82</v>
@@ -3704,19 +3745,19 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>83</v>
@@ -3741,29 +3782,29 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3787,10 +3828,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3798,45 +3839,47 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>202</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>205</v>
-      </c>
       <c r="O16" t="s" s="2">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3861,13 +3904,11 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3885,13 +3926,13 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
@@ -3900,30 +3941,30 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>211</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3946,13 +3987,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4003,7 +4044,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4027,7 +4068,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4038,10 +4079,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4070,7 +4111,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4111,19 +4152,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4147,7 +4188,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4158,10 +4199,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4184,19 +4225,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4245,7 +4286,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4266,10 +4307,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4280,10 +4321,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4306,13 +4347,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4363,7 +4404,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4387,7 +4428,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4398,10 +4439,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4430,7 +4471,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4471,19 +4512,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4507,7 +4548,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4518,10 +4559,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4529,7 +4570,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -4547,23 +4588,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4605,7 +4646,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4626,10 +4667,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4640,10 +4681,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4666,16 +4707,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4725,7 +4766,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4746,10 +4787,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4760,10 +4801,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4771,7 +4812,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
@@ -4789,21 +4830,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4845,7 +4886,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4866,10 +4907,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4880,10 +4921,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4906,17 +4947,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4965,7 +5006,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4986,10 +5027,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5000,10 +5041,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5026,19 +5067,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5087,7 +5128,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5108,10 +5149,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5122,10 +5163,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5148,19 +5189,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5209,7 +5250,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5230,10 +5271,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5244,24 +5285,24 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>83</v>
@@ -5270,19 +5311,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5307,13 +5348,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>83</v>
+        <v>292</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5331,10 +5372,10 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>94</v>
@@ -5346,30 +5387,30 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5380,7 +5421,7 @@
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>83</v>
@@ -5389,20 +5430,18 @@
         <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>298</v>
+        <v>207</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>299</v>
+        <v>208</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5451,19 +5490,19 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>297</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>83</v>
@@ -5472,13 +5511,13 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>302</v>
+        <v>211</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
@@ -5486,21 +5525,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>304</v>
+        <v>139</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>83</v>
@@ -5509,23 +5548,21 @@
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>305</v>
+        <v>140</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>306</v>
+        <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>307</v>
+        <v>214</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>83</v>
       </c>
@@ -5561,46 +5598,46 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>303</v>
+        <v>217</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>310</v>
+        <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>312</v>
+        <v>211</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
@@ -5608,21 +5645,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>315</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>83</v>
@@ -5634,19 +5671,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>316</v>
+        <v>220</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>317</v>
+        <v>221</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>318</v>
+        <v>222</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>319</v>
+        <v>223</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>320</v>
+        <v>224</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5695,13 +5732,13 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>225</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
@@ -5710,19 +5747,19 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>321</v>
+        <v>83</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>322</v>
+        <v>226</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>323</v>
+        <v>227</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
@@ -5730,10 +5767,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5753,20 +5790,18 @@
         <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>326</v>
+        <v>207</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>327</v>
+        <v>208</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5815,7 +5850,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>210</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5827,7 +5862,7 @@
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>83</v>
@@ -5836,13 +5871,13 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>330</v>
+        <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>331</v>
+        <v>211</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -5850,14 +5885,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>333</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>333</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5873,23 +5908,21 @@
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>334</v>
+        <v>140</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>335</v>
+        <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>336</v>
+        <v>214</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
@@ -5925,19 +5958,19 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>333</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5949,22 +5982,22 @@
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>339</v>
+        <v>83</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>340</v>
+        <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>341</v>
+        <v>211</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>342</v>
+        <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -5972,10 +6005,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>343</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>343</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5989,7 +6022,7 @@
         <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>83</v>
@@ -5998,26 +6031,26 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>217</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>344</v>
+        <v>234</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>345</v>
+        <v>235</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>346</v>
+        <v>236</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>347</v>
+        <v>237</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6059,7 +6092,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>343</v>
+        <v>239</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6068,7 +6101,7 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>348</v>
+        <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
@@ -6077,27 +6110,27 @@
         <v>83</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>349</v>
+        <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>351</v>
+        <v>241</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>352</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>353</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>353</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6117,23 +6150,21 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>354</v>
+        <v>244</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>355</v>
+        <v>245</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6157,13 +6188,13 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>358</v>
+        <v>83</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>359</v>
+        <v>83</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>360</v>
+        <v>83</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6181,7 +6212,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>353</v>
+        <v>247</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6190,7 +6221,7 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>361</v>
+        <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>106</v>
@@ -6202,10 +6233,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>137</v>
+        <v>248</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>362</v>
+        <v>249</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6216,21 +6247,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>363</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>363</v>
+        <v>308</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>364</v>
+        <v>83</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6239,29 +6270,27 @@
         <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>193</v>
+        <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>365</v>
+        <v>252</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>368</v>
+        <v>254</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6279,13 +6308,13 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>358</v>
+        <v>83</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>369</v>
+        <v>83</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>370</v>
+        <v>83</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -6303,13 +6332,13 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>363</v>
+        <v>256</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
@@ -6321,27 +6350,27 @@
         <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>372</v>
+        <v>257</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>373</v>
+        <v>258</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>374</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>375</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>375</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6352,7 +6381,7 @@
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>83</v>
@@ -6361,22 +6390,20 @@
         <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>376</v>
+        <v>207</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>377</v>
+        <v>261</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>380</v>
+        <v>263</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6425,13 +6452,13 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>375</v>
+        <v>264</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>83</v>
@@ -6446,10 +6473,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>381</v>
+        <v>265</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>382</v>
+        <v>266</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6460,10 +6487,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>383</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>383</v>
+        <v>311</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6483,21 +6510,23 @@
         <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>384</v>
+        <v>270</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>385</v>
+        <v>271</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6521,13 +6550,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>387</v>
+        <v>83</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6545,7 +6574,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>383</v>
+        <v>274</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6563,27 +6592,27 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>390</v>
+        <v>275</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>391</v>
+        <v>276</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>392</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>393</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>393</v>
+        <v>312</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6603,22 +6632,22 @@
         <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>394</v>
+        <v>279</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>395</v>
+        <v>280</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>396</v>
+        <v>281</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>397</v>
+        <v>282</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6643,13 +6672,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>398</v>
+        <v>83</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>399</v>
+        <v>83</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6667,7 +6696,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>393</v>
+        <v>283</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6688,10 +6717,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>400</v>
+        <v>284</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>401</v>
+        <v>285</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6702,10 +6731,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>402</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>402</v>
+        <v>313</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6719,27 +6748,29 @@
         <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>403</v>
+        <v>314</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>404</v>
+        <v>315</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>405</v>
+        <v>315</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6787,7 +6818,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>402</v>
+        <v>313</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6802,30 +6833,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>407</v>
+        <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>408</v>
+        <v>319</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>409</v>
+        <v>320</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>83</v>
+        <v>321</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>410</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>411</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>411</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6836,7 +6867,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>83</v>
@@ -6845,19 +6876,19 @@
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>412</v>
+        <v>323</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>413</v>
+        <v>324</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>414</v>
+        <v>324</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>415</v>
+        <v>325</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6907,13 +6938,13 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>411</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>83</v>
@@ -6925,38 +6956,38 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>416</v>
+        <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>417</v>
+        <v>296</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>418</v>
+        <v>326</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>83</v>
+        <v>321</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>420</v>
+        <v>327</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>420</v>
+        <v>327</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>83</v>
+        <v>328</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -6965,22 +6996,22 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>421</v>
+        <v>329</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>422</v>
+        <v>330</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>423</v>
+        <v>330</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>424</v>
+        <v>331</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>425</v>
+        <v>332</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7029,34 +7060,34 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>420</v>
+        <v>327</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>426</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>427</v>
+        <v>334</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>428</v>
+        <v>335</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7064,14 +7095,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>429</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>429</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>83</v>
+        <v>338</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7087,19 +7118,23 @@
         <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>217</v>
+        <v>339</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>218</v>
+        <v>340</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7147,7 +7182,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>220</v>
+        <v>337</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7159,22 +7194,22 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>83</v>
+        <v>343</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>83</v>
+        <v>344</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>221</v>
+        <v>345</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>83</v>
+        <v>346</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7182,21 +7217,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>430</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>430</v>
+        <v>347</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7205,19 +7240,19 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>140</v>
+        <v>348</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>141</v>
+        <v>349</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>223</v>
+        <v>349</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>143</v>
+        <v>350</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7267,19 +7302,19 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7288,13 +7323,13 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>83</v>
+        <v>351</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>221</v>
+        <v>352</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>83</v>
+        <v>353</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7302,14 +7337,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>431</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>431</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>432</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7322,25 +7357,25 @@
         <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>140</v>
+        <v>355</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>433</v>
+        <v>356</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>434</v>
+        <v>356</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>143</v>
+        <v>357</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>149</v>
+        <v>358</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7389,7 +7424,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>435</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7401,22 +7436,22 @@
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>83</v>
+        <v>359</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>83</v>
+        <v>360</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>137</v>
+        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7424,10 +7459,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7441,25 +7476,29 @@
         <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>437</v>
+        <v>207</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>438</v>
+        <v>364</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7507,7 +7546,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>436</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7516,7 +7555,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>440</v>
+        <v>367</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7525,27 +7564,27 @@
         <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>83</v>
+        <v>368</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>441</v>
+        <v>369</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>442</v>
+        <v>370</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7568,16 +7607,20 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>437</v>
+        <v>189</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>444</v>
+        <v>373</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7601,13 +7644,13 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>83</v>
+        <v>377</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7625,7 +7668,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7634,7 +7677,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>440</v>
+        <v>379</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7646,10 +7689,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>441</v>
+        <v>137</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>446</v>
+        <v>380</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7660,21 +7703,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>381</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>381</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>83</v>
+        <v>382</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7686,19 +7729,19 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>448</v>
+        <v>383</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>449</v>
+        <v>383</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>450</v>
+        <v>384</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>451</v>
+        <v>385</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7723,13 +7766,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>118</v>
+        <v>376</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>452</v>
+        <v>386</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>453</v>
+        <v>387</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7747,13 +7790,13 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>447</v>
+        <v>381</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>83</v>
@@ -7765,27 +7808,27 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>454</v>
+        <v>388</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>455</v>
+        <v>389</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>456</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>456</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7808,19 +7851,19 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>193</v>
+        <v>393</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>457</v>
+        <v>394</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>458</v>
+        <v>394</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>459</v>
+        <v>395</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>460</v>
+        <v>396</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7845,13 +7888,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>461</v>
+        <v>83</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>462</v>
+        <v>83</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7869,7 +7912,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>456</v>
+        <v>392</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7887,13 +7930,13 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>454</v>
+        <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>455</v>
+        <v>397</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7904,10 +7947,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>463</v>
+        <v>399</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>463</v>
+        <v>399</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7930,18 +7973,18 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>464</v>
+        <v>189</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>465</v>
+        <v>400</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>83</v>
       </c>
@@ -7965,13 +8008,11 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -7989,7 +8030,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>463</v>
+        <v>399</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8007,27 +8048,27 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>83</v>
+        <v>403</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>83</v>
+        <v>404</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>468</v>
+        <v>405</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>83</v>
+        <v>406</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>469</v>
+        <v>407</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>469</v>
+        <v>407</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8050,16 +8091,20 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>470</v>
+        <v>408</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8083,13 +8128,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>83</v>
+        <v>411</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>83</v>
+        <v>412</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8107,7 +8152,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>469</v>
+        <v>407</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8128,10 +8173,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>441</v>
+        <v>413</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>472</v>
+        <v>414</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8142,10 +8187,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>473</v>
+        <v>415</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>473</v>
+        <v>415</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8156,7 +8201,7 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
@@ -8165,19 +8210,19 @@
         <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>474</v>
+        <v>416</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>475</v>
+        <v>417</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>476</v>
+        <v>417</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>477</v>
+        <v>418</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8227,13 +8272,13 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>473</v>
+        <v>415</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
@@ -8245,27 +8290,27 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>478</v>
+        <v>420</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>479</v>
+        <v>421</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>83</v>
+        <v>422</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>480</v>
+        <v>423</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>480</v>
+        <v>423</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8276,7 +8321,7 @@
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>83</v>
@@ -8285,19 +8330,19 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>172</v>
+        <v>424</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>481</v>
+        <v>425</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>482</v>
+        <v>425</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>483</v>
+        <v>426</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8347,13 +8392,13 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>480</v>
+        <v>423</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>83</v>
@@ -8365,27 +8410,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>83</v>
+        <v>427</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>478</v>
+        <v>428</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>484</v>
+        <v>429</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>83</v>
+        <v>430</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>485</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>485</v>
+        <v>431</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8405,22 +8450,22 @@
         <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>486</v>
+        <v>433</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>487</v>
+        <v>433</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>488</v>
+        <v>434</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>489</v>
+        <v>435</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8469,7 +8514,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>485</v>
+        <v>431</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8481,7 +8526,7 @@
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>436</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>83</v>
@@ -8490,10 +8535,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>490</v>
+        <v>437</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>491</v>
+        <v>438</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8504,10 +8549,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>492</v>
+        <v>439</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>492</v>
+        <v>439</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8530,13 +8575,13 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8587,7 +8632,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8611,7 +8656,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8622,10 +8667,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>493</v>
+        <v>440</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>493</v>
+        <v>440</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8654,7 +8699,7 @@
         <v>141</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>143</v>
@@ -8707,7 +8752,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8731,7 +8776,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8742,14 +8787,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>494</v>
+        <v>441</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>494</v>
+        <v>441</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8771,10 +8816,10 @@
         <v>140</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -8829,7 +8874,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8864,10 +8909,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>495</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>495</v>
+        <v>446</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8875,7 +8920,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>94</v>
@@ -8887,23 +8932,19 @@
         <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>193</v>
+        <v>447</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>496</v>
+        <v>448</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
@@ -8927,13 +8968,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -8951,16 +8992,16 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>495</v>
+        <v>446</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>83</v>
+        <v>450</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -8969,16 +9010,16 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>499</v>
+        <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>212</v>
+        <v>451</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>213</v>
+        <v>452</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -8986,10 +9027,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>500</v>
+        <v>453</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>500</v>
+        <v>453</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9009,23 +9050,19 @@
         <v>83</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>501</v>
+        <v>447</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>502</v>
+        <v>454</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9073,7 +9110,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>500</v>
+        <v>453</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9082,7 +9119,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>83</v>
+        <v>450</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9091,27 +9128,27 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>504</v>
+        <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>350</v>
+        <v>451</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>351</v>
+        <v>456</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>352</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>505</v>
+        <v>457</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>505</v>
+        <v>457</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9134,19 +9171,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>506</v>
+        <v>458</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>507</v>
+        <v>459</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>508</v>
+        <v>460</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>357</v>
+        <v>461</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9171,13 +9208,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>358</v>
+        <v>118</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>359</v>
+        <v>462</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>360</v>
+        <v>463</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9195,7 +9232,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>505</v>
+        <v>457</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9204,7 +9241,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>361</v>
+        <v>83</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9213,13 +9250,13 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>83</v>
+        <v>464</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>137</v>
+        <v>465</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9230,14 +9267,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>509</v>
+        <v>466</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>509</v>
+        <v>466</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>364</v>
+        <v>83</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9256,19 +9293,19 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>365</v>
+        <v>467</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>366</v>
+        <v>468</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>367</v>
+        <v>469</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>368</v>
+        <v>470</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9293,13 +9330,13 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>358</v>
+        <v>291</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>369</v>
+        <v>471</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>370</v>
+        <v>472</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9317,7 +9354,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>509</v>
+        <v>466</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9335,27 +9372,27 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>371</v>
+        <v>464</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>372</v>
+        <v>465</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>374</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9366,7 +9403,7 @@
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
@@ -9378,19 +9415,17 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>84</v>
+        <v>474</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>511</v>
+        <v>475</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>425</v>
+        <v>477</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9439,13 +9474,13 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>83</v>
@@ -9460,20 +9495,1470 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>427</v>
+        <v>83</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>428</v>
+        <v>478</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP62">
+  <autoFilter ref="A1:AP74">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9483,7 +10968,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -93,7 +93,8 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright JED-Project、JAHIS、日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG  
+This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995+, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -286,7 +286,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1188,7 +1188,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1374,7 +1374,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1630,7 +1630,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -2007,7 +2007,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="63.09375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -1445,7 +1445,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -1983,17 +1983,17 @@
   <dimension ref="A1:AP74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="176.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="151.41015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2002,28 +2002,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.09375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.09375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2877" uniqueCount="528">
   <si>
     <t>Property</t>
   </si>
@@ -1268,7 +1268,10 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -8011,9 +8014,11 @@
       <c r="X50" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Y50" s="2"/>
+      <c r="Y50" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8049,27 +8054,27 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8095,16 +8100,16 @@
         <v>189</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8132,10 +8137,10 @@
         <v>291</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8153,7 +8158,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8174,10 +8179,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8188,10 +8193,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8214,16 +8219,16 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8273,7 +8278,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8291,27 +8296,27 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8334,16 +8339,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8393,7 +8398,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8411,27 +8416,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8454,19 +8459,19 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8515,7 +8520,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8527,7 +8532,7 @@
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>83</v>
@@ -8536,10 +8541,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8550,10 +8555,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8668,10 +8673,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8788,14 +8793,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8817,10 +8822,10 @@
         <v>140</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -8875,7 +8880,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8910,10 +8915,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8936,13 +8941,13 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8993,7 +8998,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9002,7 +9007,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9014,10 +9019,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9028,10 +9033,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9054,13 +9059,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9111,7 +9116,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9120,7 +9125,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9132,10 +9137,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9146,10 +9151,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9175,16 +9180,16 @@
         <v>189</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9212,10 +9217,10 @@
         <v>118</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9233,7 +9238,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9251,10 +9256,10 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>390</v>
@@ -9268,10 +9273,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9297,16 +9302,16 @@
         <v>189</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9334,10 +9339,10 @@
         <v>291</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9355,7 +9360,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9373,10 +9378,10 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>390</v>
@@ -9390,10 +9395,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9416,17 +9421,17 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9475,7 +9480,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9499,7 +9504,7 @@
         <v>83</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9510,10 +9515,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9539,10 +9544,10 @@
         <v>207</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9593,7 +9598,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9614,10 +9619,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9628,10 +9633,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9654,16 +9659,16 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9713,7 +9718,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9734,10 +9739,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9748,10 +9753,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9777,13 +9782,13 @@
         <v>170</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9833,7 +9838,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9854,10 +9859,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9868,10 +9873,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9894,19 +9899,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -9955,7 +9960,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9976,10 +9981,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -9990,10 +9995,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10108,10 +10113,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10228,14 +10233,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10257,10 +10262,10 @@
         <v>140</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>143</v>
@@ -10315,7 +10320,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10350,10 +10355,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10379,13 +10384,13 @@
         <v>189</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O70" t="s" s="2">
         <v>290</v>
@@ -10437,7 +10442,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>94</v>
@@ -10455,7 +10460,7 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>296</v>
@@ -10472,10 +10477,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10498,16 +10503,16 @@
         <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>366</v>
@@ -10559,7 +10564,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10577,7 +10582,7 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>369</v>
@@ -10594,10 +10599,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10623,13 +10628,13 @@
         <v>189</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>375</v>
@@ -10681,7 +10686,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10716,10 +10721,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10745,16 +10750,16 @@
         <v>189</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10803,7 +10808,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10838,10 +10843,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10867,16 +10872,16 @@
         <v>84</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10925,7 +10930,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10946,10 +10951,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -387,7 +387,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -624,7 +624,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -927,7 +927,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1018,7 +1018,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1191,7 +1191,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1220,7 +1220,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1271,7 +1271,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1301,7 +1301,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1338,7 +1338,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1413,7 +1413,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1463,7 +1463,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1496,7 +1496,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright JED-Project、JAHIS、日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG  
+    <t>Copyright JED-Project、JAHIS、日本医療情報学会FHIR国内実装基盤研究会  
 This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995+, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc</t>
   </si>
   <si>
@@ -3237,7 +3237,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>151</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>199</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>313</v>
       </c>
@@ -7461,7 +7461,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>363</v>
       </c>
@@ -10965,12 +10965,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP74">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -627,7 +627,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -1345,7 +1345,7 @@
     <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
   </si>
   <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
+    <t>これは、結果の送信に関与する機器（ゲートウェイなど）を表すことを意図したものではない。そのような機器は、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -655,6 +655,14 @@
     <t>このObservationを分類するコード。(imaging)が指定される。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="imaging"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -809,9 +817,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>imaging</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -3893,7 +3898,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3912,7 +3917,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3965,10 +3970,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3991,13 +3996,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4048,7 +4053,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4072,7 +4077,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4083,10 +4088,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4115,7 +4120,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4156,10 +4161,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4168,7 +4173,7 @@
         <v>196</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4192,7 +4197,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4203,10 +4208,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4229,19 +4234,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4290,7 +4295,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4311,10 +4316,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4325,10 +4330,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4351,13 +4356,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4408,7 +4413,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4432,7 +4437,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4443,10 +4448,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4475,7 +4480,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4516,10 +4521,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -4528,7 +4533,7 @@
         <v>196</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4552,7 +4557,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4563,10 +4568,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4592,23 +4597,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4650,7 +4655,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4671,10 +4676,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4685,10 +4690,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4711,16 +4716,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4770,7 +4775,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4791,10 +4796,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4805,10 +4810,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4834,21 +4839,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>255</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4951,7 +4956,7 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>261</v>
@@ -5193,7 +5198,7 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>279</v>
@@ -5437,13 +5442,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5494,7 +5499,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5518,7 +5523,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5561,7 +5566,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5602,10 +5607,10 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
@@ -5614,7 +5619,7 @@
         <v>196</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5638,7 +5643,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5675,19 +5680,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5736,7 +5741,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5757,10 +5762,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5797,13 +5802,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5854,7 +5859,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5878,7 +5883,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5921,7 +5926,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -5962,10 +5967,10 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
@@ -5974,7 +5979,7 @@
         <v>196</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5998,7 +6003,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6038,16 +6043,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6096,7 +6101,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6117,10 +6122,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6157,16 +6162,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6216,7 +6221,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6237,10 +6242,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6280,14 +6285,14 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6397,7 +6402,7 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>261</v>
@@ -6639,7 +6644,7 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>279</v>
@@ -7489,7 +7494,7 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>364</v>
@@ -8581,13 +8586,13 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8638,7 +8643,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8662,7 +8667,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8705,7 +8710,7 @@
         <v>141</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>143</v>
@@ -8758,7 +8763,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8782,7 +8787,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -9541,7 +9546,7 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>481</v>
@@ -10021,13 +10026,13 @@
         <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10078,7 +10083,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10102,7 +10107,7 @@
         <v>83</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10145,7 +10150,7 @@
         <v>141</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>143</v>
@@ -10198,7 +10203,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10222,7 +10227,7 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -1030,7 +1030,7 @@
     <t>配偶者、親、胎児、ドナーなど、このObservationのsubject要素が実際の対象でない場合、その実際の対象に関する情報</t>
   </si>
   <si>
-    <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
+    <t>通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1575,7 +1575,7 @@
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
   </si>
   <si>
-    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
+    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではない）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
